--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_014/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -725,46 +730,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1121,6 +1086,11 @@
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1403,12 +1373,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Preclinical micromotion and rim contact screening of porous Ti-6Al-4V acetabular shell for primary hip arthroplasty</t>
+          <t>Preclinical screening of porous Ti-6Al-4V acetabular shell for primary hips under gait loading</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>FE model used to predict interface micromotion and local stresses under gait loading to inform go/no-go decision for cadaveric testing and design freeze of the Alpha-52 acetabular cup. Applicable to shell sizes 48–56 mm, primary hips, bone quality T-score −1 to −2, loads up to 1.5 kN/30 N·m, seating misalignment ±2°.</t>
+          <t>FEA-based structural model used to evaluate interface micromotion and rim contact conditions for a 52 mm cementless acetabular cup under worst-case stance-phase loading. The model informs a go/no-go decision for design freeze and cadaveric testing. Applicability covers shell sizes 48–56 mm, primary hips, bone quality T-score −1 to −2, loads up to 1.5 kN and 30 N·m torque, and seating misalignment within ±2°.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1446,9 +1416,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2044,7 +2014,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>CQ-AC-052 Micromotion and Contact Screening Requirement</t>
+          <t>Micromotion and Contact Screening Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2054,7 +2024,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model predictions of interface micromotion must support go/no-go to cadaveric testing; 95th-percentile micromotion must remain below 50 µm osseointegration threshold; validated micromotion error target ≤10%; local stress screening accuracy ±20% acceptable</t>
+          <t>Model must predict interface micromotion with sufficient fidelity (validated error ≤ ~10%, 95th-percentile micromotion &lt; 50 µm osseointegration threshold) and contact footprint within acceptable tolerance to support design-freeze and cadaveric test go/no-go decision for Alpha-52 cup.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2076,13 +2046,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Alpha-52 ANSYS Structural FE Model</t>
+          <t>ANSYS Mechanical FEA Model — Alpha-52 Acetabular Cup</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Mechanical 2023 R2 TET10 model of 52 mm porous Ti-6Al-4V acetabular shell seated in pelvis segment; linear elastic bone and cup, frictional contact, Augmented Lagrange, large-deflection enabled</t>
+          <t>TET10 finite element model of 52 mm porous Ti-6Al-4V shell seated in pelvis CT-derived geometry; Augmented Lagrange contact, Newton–Raphson solver, Latin hypercube UQ over key inputs.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2096,13 +2066,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Foam and Cadaveric Pelvis Validation Dataset</t>
+          <t>Foam Hemipelvis and Cadaveric Validation Dataset</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Six 20 pcf foam hemipelvis blocks and two cadaveric pelves (T-scores −1.1, −2.0); interface slip measured at six rim points via LVDTs and DIC; contact footprint from Fuji film imprints under 1.5 kN + 30 N·m loading</t>
+          <t>Six 20 pcf foam hemipelvis blocks and two cadaveric pelves (T-scores −1.1, −2.0); LVDT and DIC displacement measurements at six rim points; Fuji film contact imprints under 1.5 kN and 30 N·m torque loading.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2122,7 +2092,7 @@
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V properties from ASTM F136; CT-derived Hounsfield-to-modulus mapping per Keyak; seating misalignment tolerances ±2°; initial gap distribution normal(50 µm, σ=30 µm); calibrated friction coefficient μ=0.56 ± 0.08 from push-out tests</t>
+          <t>Ti-6Al-4V properties per ASTM F136 (E = 110 GPa, ν = 0.34); bone E(ρ) from Hounsfield-to-modulus (Keyak); seating misalignment ±2° from build/jig tolerances; initial gap normal(50 µm, σ = 30 µm); calibrated friction coefficient μ = 0.56 ± 0.08 from three independent push-out tests.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2272,7 +2242,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Interface Micromotion Comparison — Foam and Cadaveric Specimens</t>
+          <t>Interface Slip Regression vs. Experimental LVDT/DIC</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2287,12 +2257,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model-predicted interface slip compared against LVDT and DIC measurements at six rim points across six foam and two cadaveric hemipelvis specimens under 1.5 kN compressive + 30 N·m torque loading</t>
+          <t>Model-predicted interface slip compared against LVDT and DIC measurements at six rim points across foam and cadaveric test articles under 1.5 kN compressive load plus 30 N·m torque.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Experimental LVDT/DIC slip measurements</t>
+          <t>LVDT and DIC measurements on foam hemipelvis and cadaveric pelves</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2302,12 +2272,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Latin hypercube sampling (N=300) over μ, bone E scaling, seating angle, initial gap; Sobol first-order sensitivity indices reported</t>
+          <t>Latin hypercube sampling (N=300) over friction coefficient, bone modulus scaling, seating angle, and initial gap</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Regression slope 0.95, R²=0.93, MAPE 8% overall (9% cadaveric only); 95th-percentile micromotion 42 µm &lt; 50 µm threshold</t>
+          <t>Regression slope 0.95, R² = 0.93, mean absolute percent error 8% (overall), 9% (cadaveric only); 95th-percentile micromotion 42 µm vs. 50 µm threshold</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2319,7 +2289,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Contact Footprint Area and Centroid Comparison</t>
+          <t>Contact Footprint Comparison vs. Fuji Film Imprints</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2330,7 +2300,7 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Model-predicted contact area and centroid location compared against Fuji film pressure imprints from experimental specimens</t>
+          <t>Predicted contact area and centroid location compared against Fuji film pressure-sensitive imprints under identical loading conditions.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
@@ -2346,7 +2316,7 @@
       <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Predicted contact area within 12% of Fuji film; centroid locations within 3 mm</t>
+          <t>Contact area within 12%; centroid location within 3 mm</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2369,12 +2339,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh convergence study (0.9M, 1.3M, 1.8M elements) with Richardson extrapolation; asymptotic order and GCI computed for peak interface slip and peak von Mises stress</t>
+          <t>Three-mesh refinement study (0.9M, 1.3M, 1.8M elements) to assess discretization error; Richardson extrapolation applied; asymptotic convergence verified.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / asymptotic solution</t>
+          <t>Richardson extrapolation / asymptotic convergence criterion</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2389,7 +2359,7 @@
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Asymptotic slope ~2.1; GCI ~2% for peak interface slip; GCI ~5% for peak von Mises in cup</t>
+          <t>GCI ≈ 2% for peak interface slip; GCI ≈ 5% for peak von Mises; asymptotic slope ≈ 2.1</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2401,7 +2371,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Code Verification — Analytical Benchmark Problems</t>
+          <t>Numerical Solver Verification (Analytical Benchmarks)</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2412,12 +2382,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Mechanical verified against cantilever beam and Hertz contact analytical solutions to confirm solver correctness</t>
+          <t>Vendor patch tests and in-house benchmarks (cantilever beam, Hertz contact) run against analytical solutions to verify code correctness.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Analytical solutions (cantilever deflection, Hertz contact pressure)</t>
+          <t>Analytical solutions for cantilever displacement and Hertz contact pressure</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2428,7 +2398,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Displacement and pressure reproduced within 0.7–1.3%</t>
+          <t>Displacement error 0.7–1.3%; pressure error within same range</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2438,47 +2408,14 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>Friction Coefficient Calibration — Push-Out Tests</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
       <c r="C7" s="33" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>Effective friction coefficient μ calibrated on three independent push-out tests; holdout specimens not used for calibration; residuals checked for bias</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="inlineStr">
-        <is>
-          <t>Push-out test measurements (calibration set)</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>Parameter estimation with residual bias check</t>
-        </is>
-      </c>
-      <c r="H7" s="41" t="inlineStr">
-        <is>
-          <t>Calibrated μ = 0.56 ± 0.08; residuals unbiased</t>
-        </is>
-      </c>
-      <c r="I7" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="33" t="n"/>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="33" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="24" t="n"/>
@@ -2695,12 +2632,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; in-house scripts with version control and testing</t>
+          <t>Commercial solver with documented verification; in-house scripts under version control and CI testing</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>ANSYS Mechanical 2023 R2 is a commercial solver with vendor patch tests passed. In-house Python preprocessors have 86% unit test coverage, CI on Jenkins, all runs under Git tag sim-hip-cup@v1.7.2, seeds fixed, workstation specs logged. Vendor patch tests confirmed. Strong version control and traceability throughout.</t>
+          <t>ANSYS Mechanical 2023 R2 (commercial solver with vendor patch tests passed). In-house Python preprocessors have 86% unit test coverage with CI on Jenkins. All simulation runs tracked under Git tag sim-hip-cup@v1.7.2 with fixed seeds and logged workstation specs. Requirements-to-model-to-test traceability matrix maintained in Confluence (CQ-AC-052); input decks, meshes, and scripts archived and hash-checked.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2728,12 +2665,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Comparison to analytical solutions within acceptable tolerance for relevant physics</t>
+          <t>Analytical solution comparison within acceptable tolerance for displacement and contact pressure</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Cantilever beam and Hertz contact benchmark problems solved; displacement and pressure match analytical solutions within 0.7–1.3%. Vendor patch tests also passed. These cover the dominant physics (structural deformation and contact pressure) relevant to the COU.</t>
+          <t>Vendor patch tests confirmed passed. In-house benchmark suite includes cantilever beam (displacement error 0.7–1.3%) and Hertz contact (pressure error 0.7–1.3%) compared to analytical solutions. Results documented in the simulation report.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2761,12 +2698,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>GCI &lt; 5% for primary QoI (interface slip); mesh refinement study with at least three meshes</t>
+          <t>GCI &lt; 5% for primary QoI (interface slip); asymptotic convergence confirmed</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-mesh study (0.9M/1.3M/1.8M elements); asymptotic convergence slope ~2.1 (near theoretical); GCI ~2% for peak interface slip (primary QoI) and ~5% for peak von Mises. Final production runs use finest mesh (1.8M elements). Contact penalty sensitivity also checked (±25% causes &lt;3% change in micromotion).</t>
+          <t>Three-mesh study (0.9M, 1.3M, 1.8M elements); asymptotic slope ≈ 2.1 confirms convergence. GCI ≈ 2% for peak interface slip (primary QoI) and 5% for peak von Mises. Final runs performed on finest mesh (1.8M elements). Contact penalty sensitivity ±25% causes &lt; 3% change in micromotion.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2794,12 +2731,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Demonstrated iterative convergence to tight tolerances; global equilibrium checks</t>
+          <t>Residual tolerance documented; global reaction balance check performed; iterative convergence confirmed</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Newton–Raphson with line search; force residual tolerance 1e-6; contact penetration limit 3 µm; last two equilibrium iterations show strain energy change &lt;0.1%; global reactions match applied loads within 0.5%. Automatic stabilization disabled to avoid artificial energy dissipation. Convergence well-documented.</t>
+          <t>Newton–Raphson with line search; force residual tolerance 1e-6; contact penetration limit 3 µm; automatic stabilization disabled. Last two equilibrium iterations show strain energy change &lt; 0.1%. Global reactions match applied loads within 0.5%. Reaction balance check added following external red-team review.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2827,12 +2764,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary condition verification; mesh quality checks documented</t>
+          <t>Independent review of model setup; boundary condition and mesh quality verification; process checklist signed</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>External SME (L. Gomez, OrthoSim LLC) performed red-team readout; two actions identified and closed (contact stabilization off; reaction balance check added). Requirements-to-model-to-test traceability matrix in Confluence (CQ-AC-052). Input decks, meshes, scripts archived and hash-checked. Team training on ANSYS contact best practices with signed checklist. Post-processing sanity checks (no stress oscillations, path integration spot-checks within 4%).</t>
+          <t>External SME (L. Gomez, OrthoSim LLC) performed red-team readout; two minor actions identified and closed (contact stabilization turned off; reaction balance check added). Team trained on ANSYS contact best practices; process checklist signed. Post-processing sanity checks performed: no stress oscillations at contact edge; spot checks with path integration agree within 4%.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2860,12 +2797,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Physics assumptions justified with literature support; known limitations documented</t>
+          <t>Governing equations and constitutive choices justified; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Linear elastic assumption for bone and cup justified by literature on elastic micromotion thresholds for osseointegration (&lt;50 µm). Frictional sliding modeled with Augmented Lagrange; large-deflection enabled. Porous coating approximated by effective μ and measured compliance rather than geometric resolution — limitation acknowledged. No remodeling or press-fit plasticity — documented as a known limitation. Assumptions are clearly stated and bounded.</t>
+          <t>Linear elastic assumption for bone and cup justified by literature supporting elastic micromotion thresholds for osseointegration (&lt; 50 µm). Frictional sliding with Augmented Lagrange contact and large-deflection enabled. Porous coating approximated by effective friction coefficient and measured compliance rather than geometric resolution — acknowledged limitation. No remodeling or press-fit plasticity modeled. Severe osteoporosis, revision cases, cemented shells, long-term remodeling, and extreme torque (&gt; 40 N·m) explicitly excluded and documented in use restrictions.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2893,12 +2830,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from standards or testing; geometry from physical measurements; input uncertainties characterized</t>
+          <t>Material properties from standards/testing; boundary conditions from measurements; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V E=110 GPa, ν=0.34 from ASTM F136. Bone E(ρ) from Keyak CT-to-modulus mapping with density cutoffs. Seating misalignment ±2° from build/jig tolerances. Initial gap distribution normal(50 µm, σ=30 µm). Friction coefficient calibrated from push-out tests: μ=0.56 ± 0.08. Input uncertainty distributions defined for LHS propagation. Pedigree well-documented for all primary inputs.</t>
+          <t>Ti-6Al-4V properties from ASTM F136 (E = 110 GPa, ν = 0.34). Bone E(ρ) from CT Hounsfield units via Keyak mapping with density cutoffs. Seating misalignment ±2° based on build/jig tolerance measurements. Initial gap characterized as normal(50 µm, σ = 30 µm). Friction coefficient calibrated on three independent push-out tests (μ = 0.56 ± 0.08); holdout specimens not used for calibration and were reserved for validation. Sobol sensitivity analysis identifies μ (0.44) and bone modulus (0.31) as dominant input drivers.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2926,12 +2863,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Adequate number of specimens including clinically relevant surrogates; sample characteristics documented</t>
+          <t>Multiple specimens including biofidelic material; statistical characterization of sample properties</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Six foam hemipelvis blocks (20 pcf) and two cadaveric pelves (T-scores −1.1, −2.0) used. Foam surrogates provide controlled repeatability; cadaveric specimens provide biological relevance. T-scores documented. Load paths verified by instrumented potting. Sample size is modest (especially two cadaveric specimens), limiting statistical power, but appropriate for screening-level decision support alongside bench data.</t>
+          <t>Six foam hemipelvis blocks (20 pcf) and two cadaveric pelves (T-scores −1.1 and −2.0) used. Foam provides repeatable controlled baseline; cadaveric specimens provide biofidelic response. T-scores documented. Sample size is modest (especially cadaveric n=2) but fixtures verified and load paths confirmed by instrumented potting. Bone density characterization via T-score rather than full statistical distribution.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2959,12 +2896,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Controlled loading conditions; calibrated instrumentation; test conditions documented</t>
+          <t>Controlled and measured loading; calibrated instrumentation; boundary conditions verified</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>1.5 kN compressive + 30 N·m torque applied through hip simulator representing worst-case stance phase. Displacement measured via calibrated LVDTs and DIC at six rim points. Fixtures designed to mimic boundary stiffness; load paths verified by instrumented potting. Measurement system described but explicit instrument calibration certificates and formal measurement uncertainty quantification not detailed in the report.</t>
+          <t>Loading applied via hip simulator at 1.5 kN compressive plus 30 N·m torque representing worst-case stance phase. Displacement measured at six rim points via LVDTs and DIC. Fixtures designed to mimic boundary stiffness; load paths verified by instrumented potting. Measurement uncertainty not explicitly quantified in the report beyond instrument identification; calibration status of LVDT/DIC not explicitly stated.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2992,12 +2929,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model boundary conditions match experimental conditions; parameter matching documented</t>
+          <t>Model boundary conditions match test conditions; input parameter comparison documented</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Loading (1.5 kN + 30 N·m), geometry (52 mm shell), friction coefficient, and bone properties mapped from the same specimen characteristics used in tests. Seating misalignment range ±2° consistent with experimental fixture. Calibrated μ reused for validation articles without retuning, providing clean separation. Initial gap distribution matched to physical setup. Some uncertainty in exact cadaveric bone modulus distribution mapping noted implicitly but not fully quantified in the matching.</t>
+          <t>Model loading conditions (1.5 kN + 30 N·m) directly replicate hip simulator settings. Seating geometry and misalignment aligned with experimental fixture tolerances. Friction coefficient calibrated on independent push-out tests and reused without retuning for validation articles, demonstrating consistent input application. Initial gap distribution derived from build tolerances applied consistently. Full uncertainty propagation performed in UQ study matching physical input ranges.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3030,7 +2967,7 @@
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Interface slip: regression slope 0.95, R²=0.93, MAPE 8% overall (9% cadaveric). Contact footprint area within 12%; centroid within 3 mm. Uncertainty propagation (LHS N=300): micromotion 28 ± 7 µm at critical node, 95th percentile 42 µm vs. 50 µm threshold. Sobol sensitivity indices quantify input drivers. Multiple output types compared (slip, contact area, centroid). Calibration/validation separation maintained. Comprehensive quantitative assessment.</t>
+          <t>Interface slip comparison: regression slope 0.95, R² = 0.93, mean absolute percent error 8% overall and 9% cadaveric-only across six rim measurement points. Contact footprint: area within 12%, centroid within 3 mm vs. Fuji film imprints. LHS UQ (N=300) yields micromotion = 28 ± 7 µm at critical node with 95th percentile 42 µm, below 50 µm threshold. Residuals confirmed unbiased. Multiple metrics (slip magnitude, contact area, centroid) used.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3058,12 +2995,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the osseointegration safety and design screening decision; measurable both computationally and experimentally</t>
+          <t>QoI directly reflects osseointegration risk and contact mechanics; measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Interface micromotion directly maps to osseointegration threshold (50 µm literature limit); rim contact conditions inform fixation stability — both are the stated decision drivers for design freeze. QoIs are measurable via LVDT/DIC experimentally and directly extracted from FE output. Peak stress reported as secondary QoI for screening with explicitly relaxed accuracy requirement (±20%). QoI hierarchy clearly defined and tied to clinical relevance.</t>
+          <t>Primary QoI is interface micromotion (µm), directly linked to osseointegration threshold (&lt; 50 µm per literature). Secondary QoI is contact footprint geometry, relevant to load transfer assessment. Both quantities are directly measurable experimentally (LVDT, DIC, Fuji film) and computationally. QoI selection explicitly tied to the go/no-go decision criteria. Peak von Mises stress retained as supplementary QoI for screening but acknowledged as less decision-driving.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3091,12 +3028,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions cover the intended operating envelope; gaps documented and bounded</t>
+          <t>Validation conditions cover the intended operating envelope; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation covers 52 mm shell, T-score −1 to −2 bone quality, 1.5 kN/30 N·m loading — matching the primary COU envelope. Foam and cadaveric specimens bracket surrogate and biological response. Gaps explicitly documented: severe osteoporosis (T &lt; −2.5), revision cases, cemented shells, extreme torque &gt;40 N·m, long-term remodeling not covered. Add-on task proposed (one osteoporotic cadaver) to probe low-E tail. Validation scope is adequate for the stated applicability limits but does not fully cover the broader clinical population.</t>
+          <t>Validation covers foam and osteopenic cadaveric specimens (T-score −1.1 to −2.0) matching the stated COU bone quality range. Loading (1.5 kN, 30 N·m) matches worst-case gait scenario in COU. Shell size 52 mm tested; applicability stated for 48–56 mm by interpolation. Known gaps explicitly documented: severe osteoporosis (T &lt; −2.5), revision cases, cemented shells, remodeling, and torque &gt; 40 N·m are out of scope. One osteoporotic cadaver specimen proposed as add-on to probe low-E tail. Cadaveric sample size (n=2) limits statistical coverage of bone quality variability within the covered range.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3185,7 +3122,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The Alpha-52 structural FE model meets all stated credibility targets for the design-freeze decision. Primary QoI (interface micromotion) is validated to MAPE ~8–9% against cadaveric specimens; numerical uncertainty (GCI ~2%) is small relative to physical uncertainty; 95th-percentile micromotion (42 µm) remains below the 50 µm osseointegration threshold under full UQ propagation. Code verification, mesh convergence, and solver convergence are well-documented. Independent SME review completed with all actions closed. Model applicability limits are explicitly documented (no severe osteoporosis, no revision cases, no extreme torque). Accepted for use in design-freeze decision and proceeding to cadaveric testing series, subject to stated applicability restrictions: (1) friction data for alternative coating lot to be obtained (ETA 2 weeks); (2) orthotropic bone sensitivity spot-check planned; (3) one osteoporotic cadaver study proposed to bound the low-E tail.</t>
+          <t>The Alpha-52 structural model meets the stated credibility targets for the intended decision. The primary QoI (interface micromotion) is validated with mean absolute percent error of 8–9%, GCI of ~2%, and a UQ-based 95th-percentile prediction of 42 µm against a 50 µm threshold, providing adequate margin. Contact footprint agreement is within 12% area and 3 mm centroid. Numerical uncertainty (GCI ~2%) is small relative to physical uncertainty. All open actions from independent red-team review are closed. Known applicability limits (severe osteoporosis, revision, extreme torque) are explicitly documented. The model is accepted for design-freeze support and progression to cadaveric testing within the stated applicability envelope. Pending items (alternative coating friction data, orthotropic bone sensitivity) are noted as low-risk add-on tasks that do not affect the current decision.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3198,7 +3135,11 @@
           <t>R. Patel, Simulation Group</t>
         </is>
       </c>
-      <c r="E3" s="22" t="n"/>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="24" t="n"/>
